--- a/results/run_2/metrics_rl.xlsx
+++ b/results/run_2/metrics_rl.xlsx
@@ -503,44 +503,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LinearRegression</t>
+          <t>regression lineaire</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0009070434399469005</v>
+        <v>0.001817840417831737</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03011716188399731</v>
+        <v>0.04263613980922449</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01271243468082023</v>
+        <v>0.01843914040810124</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2320686956743607</v>
+        <v>0.4368421583624844</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0001880098207100952</v>
+        <v>0.0004931878297723691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9982505504009331</v>
+        <v>0.996091095541135</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1322208996615243</v>
+        <v>0.1877801248517948</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009070080922542169</v>
+        <v>0.001817597183596302</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03011657504189706</v>
+        <v>0.04263328727175869</v>
       </c>
       <c r="K2" t="n">
-        <v>7.138643098826362e-05</v>
+        <v>3.357123585351209e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004436500001247623</v>
+        <v>0.01499539999986155</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003819000012299512</v>
+        <v>0.000812499999483407</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
